--- a/data/trans_orig/P05A01-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P05A01-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2007</t>
+          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2007 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>206131</t>
+          <t>208235</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>254433</t>
+          <t>252877</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>130503</t>
+          <t>131065</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>167506</t>
+          <t>166928</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>351172</t>
+          <t>351811</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>406974</t>
+          <t>408924</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,45%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>152712</t>
+          <t>155509</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>200341</t>
+          <t>198115</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>100728</t>
+          <t>101433</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>134092</t>
+          <t>135646</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>266758</t>
+          <t>263790</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>323124</t>
+          <t>322363</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,35%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52122</t>
+          <t>51301</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>82159</t>
+          <t>82170</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29458</t>
+          <t>28624</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53149</t>
+          <t>52078</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>86576</t>
+          <t>88608</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>127048</t>
+          <t>127356</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>174376</t>
+          <t>175131</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>213026</t>
+          <t>213927</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>155980</t>
+          <t>156777</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>195625</t>
+          <t>194961</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>340825</t>
+          <t>342186</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>396942</t>
+          <t>398728</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>54,04%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>117895</t>
+          <t>118585</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>155651</t>
+          <t>156423</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>125939</t>
+          <t>127931</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>164552</t>
+          <t>165643</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>257602</t>
+          <t>256439</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>310750</t>
+          <t>308196</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>41,77%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25975</t>
+          <t>26144</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50846</t>
+          <t>49838</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37675</t>
+          <t>37178</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64115</t>
+          <t>63721</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68588</t>
+          <t>67558</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104144</t>
+          <t>104752</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>258379</t>
+          <t>257591</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>304754</t>
+          <t>307955</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>77672</t>
+          <t>75566</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>101489</t>
+          <t>102469</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>343800</t>
+          <t>345033</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>397908</t>
+          <t>400035</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>56,33%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>186490</t>
+          <t>185521</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>231229</t>
+          <t>233276</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37114</t>
+          <t>37099</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58786</t>
+          <t>60552</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>228375</t>
+          <t>227858</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>282584</t>
+          <t>282759</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,82%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39481</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67913</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20913</t>
+          <t>21676</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40286</t>
+          <t>41781</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67101</t>
+          <t>66597</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>101566</t>
+          <t>102252</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>603093</t>
+          <t>604943</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>676497</t>
+          <t>673814</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>324886</t>
+          <t>321765</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>377669</t>
+          <t>377964</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>940731</t>
+          <t>946036</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1035003</t>
+          <t>1034367</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,02%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>447248</t>
+          <t>448563</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>517405</t>
+          <t>515243</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>231219</t>
+          <t>231618</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>279681</t>
+          <t>282901</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>695308</t>
+          <t>697433</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>782250</t>
+          <t>781099</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,04%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96114</t>
+          <t>96069</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>135409</t>
+          <t>138700</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>91227</t>
+          <t>89467</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>129191</t>
+          <t>127755</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>196380</t>
+          <t>193312</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>252348</t>
+          <t>251498</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>190854</t>
+          <t>191486</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>229448</t>
+          <t>230438</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>271985</t>
+          <t>270604</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>320266</t>
+          <t>319552</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>474594</t>
+          <t>480054</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>536411</t>
+          <t>539689</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,77%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>88073</t>
+          <t>88087</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>123912</t>
+          <t>122013</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>176310</t>
+          <t>177462</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>224049</t>
+          <t>222041</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>276183</t>
+          <t>275906</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>334867</t>
+          <t>332727</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,23%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24791</t>
+          <t>24258</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47372</t>
+          <t>47265</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>57273</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91367</t>
+          <t>90702</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>88176</t>
+          <t>88348</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>128076</t>
+          <t>128194</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>154940</t>
+          <t>155225</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>188337</t>
+          <t>187643</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>601467</t>
+          <t>602934</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>671484</t>
+          <t>670810</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>766682</t>
+          <t>768748</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>843103</t>
+          <t>845267</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,67%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>89991</t>
+          <t>88843</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>119815</t>
+          <t>120854</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>422247</t>
+          <t>422018</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>489683</t>
+          <t>487805</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>525762</t>
+          <t>524346</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>598625</t>
+          <t>595530</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,52%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14606</t>
+          <t>15570</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>32683</t>
+          <t>35424</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>133100</t>
+          <t>134052</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>178080</t>
+          <t>178955</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>154018</t>
+          <t>154539</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>201064</t>
+          <t>205091</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1660433</t>
+          <t>1671489</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1781509</t>
+          <t>1781747</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1641052</t>
+          <t>1642543</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1754769</t>
+          <t>1754441</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3338656</t>
+          <t>3335901</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3501153</t>
+          <t>3507663</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,8%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1161560</t>
+          <t>1164497</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1273715</t>
+          <t>1271006</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1164296</t>
+          <t>1167844</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1277782</t>
+          <t>1277927</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2359695</t>
+          <t>2352707</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2519208</t>
+          <t>2512033</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,82%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>296574</t>
+          <t>292771</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>364600</t>
+          <t>363188</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>417989</t>
+          <t>417152</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>499226</t>
+          <t>493668</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>725190</t>
+          <t>726108</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>834385</t>
+          <t>832145</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2012</t>
+          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2012 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>257410</t>
+          <t>255060</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>299782</t>
+          <t>298295</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>210791</t>
+          <t>211545</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>245052</t>
+          <t>243288</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>478547</t>
+          <t>479857</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>531534</t>
+          <t>533997</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>71,04%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>106765</t>
+          <t>105094</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>146425</t>
+          <t>146280</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51787</t>
+          <t>52990</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>83224</t>
+          <t>84040</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>167330</t>
+          <t>167971</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>217449</t>
+          <t>219649</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,22%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23912</t>
+          <t>24559</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45519</t>
+          <t>47374</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13587</t>
+          <t>12749</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30329</t>
+          <t>29208</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>39946</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>68391</t>
+          <t>68246</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>257003</t>
+          <t>256575</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>297789</t>
+          <t>298310</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>212589</t>
+          <t>214601</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>247972</t>
+          <t>249110</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>480586</t>
+          <t>482175</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>536848</t>
+          <t>536478</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,05%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96439</t>
+          <t>95555</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>134415</t>
+          <t>137093</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>59149</t>
+          <t>57742</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>89172</t>
+          <t>88966</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>164248</t>
+          <t>163146</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>215188</t>
+          <t>212876</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16549</t>
+          <t>15885</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39140</t>
+          <t>38570</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21446</t>
+          <t>20845</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45483</t>
+          <t>44527</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41822</t>
+          <t>43326</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73894</t>
+          <t>75997</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>407070</t>
+          <t>407386</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>456219</t>
+          <t>456349</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>162202</t>
+          <t>162526</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>192648</t>
+          <t>193143</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>580747</t>
+          <t>582044</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>640231</t>
+          <t>639744</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,2%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>133540</t>
+          <t>134119</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>178802</t>
+          <t>178794</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46258</t>
+          <t>44781</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74349</t>
+          <t>72787</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>186087</t>
+          <t>184872</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>237889</t>
+          <t>240431</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28858</t>
+          <t>28300</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55225</t>
+          <t>55063</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14725</t>
+          <t>15116</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34321</t>
+          <t>33789</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>46797</t>
+          <t>48765</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>79812</t>
+          <t>79472</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>773234</t>
+          <t>777584</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>840903</t>
+          <t>839355</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>509856</t>
+          <t>511685</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>563398</t>
+          <t>565195</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1300383</t>
+          <t>1298261</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1385515</t>
+          <t>1386064</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,16%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>243503</t>
+          <t>243921</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>302644</t>
+          <t>301376</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>153005</t>
+          <t>154105</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>202585</t>
+          <t>203621</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>412794</t>
+          <t>413240</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>492847</t>
+          <t>491778</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58662</t>
+          <t>58695</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>95226</t>
+          <t>94517</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35904</t>
+          <t>37686</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>65143</t>
+          <t>66573</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>103134</t>
+          <t>104161</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>148987</t>
+          <t>150996</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>348321</t>
+          <t>348655</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>388742</t>
+          <t>388491</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>527004</t>
+          <t>526593</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>577086</t>
+          <t>577647</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>887975</t>
+          <t>886305</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>953204</t>
+          <t>950263</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>74,76%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>93402</t>
+          <t>93675</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>130442</t>
+          <t>132258</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>133432</t>
+          <t>135945</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>182172</t>
+          <t>181943</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>241119</t>
+          <t>241734</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>303126</t>
+          <t>303855</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,9%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21176</t>
+          <t>20328</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43344</t>
+          <t>41965</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38005</t>
+          <t>37206</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67482</t>
+          <t>66527</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64602</t>
+          <t>64127</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>99269</t>
+          <t>100147</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>159369</t>
+          <t>158257</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>188911</t>
+          <t>189334</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>733597</t>
+          <t>732123</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>794664</t>
+          <t>790747</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>899286</t>
+          <t>901331</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>966430</t>
+          <t>970132</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,55%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>66772</t>
+          <t>67258</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>95433</t>
+          <t>97642</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>256956</t>
+          <t>255755</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>315191</t>
+          <t>311875</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>336781</t>
+          <t>332509</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>402954</t>
+          <t>397845</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>28,93%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>6676</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20714</t>
+          <t>20338</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>47980</t>
+          <t>46798</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>78696</t>
+          <t>78129</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>60905</t>
+          <t>59046</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>93346</t>
+          <t>92285</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2275204</t>
+          <t>2283773</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2392215</t>
+          <t>2389247</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2433316</t>
+          <t>2432946</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2543392</t>
+          <t>2545034</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4748468</t>
+          <t>4752532</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4910492</t>
+          <t>4912214</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,58%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>806550</t>
+          <t>807569</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>915692</t>
+          <t>910796</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>770922</t>
+          <t>769541</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>870535</t>
+          <t>871981</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1605749</t>
+          <t>1608738</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1754630</t>
+          <t>1751928</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>189099</t>
+          <t>189913</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>247395</t>
+          <t>250652</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>207569</t>
+          <t>207912</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>270149</t>
+          <t>268907</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>411079</t>
+          <t>412848</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>495829</t>
+          <t>495219</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -7390,7 +7390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2016</t>
+          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>299396</t>
+          <t>300546</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>336751</t>
+          <t>339167</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>222802</t>
+          <t>223536</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>257853</t>
+          <t>259287</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>533529</t>
+          <t>534066</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>585348</t>
+          <t>586777</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,71%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70170</t>
+          <t>68908</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104027</t>
+          <t>102873</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59158</t>
+          <t>59006</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90011</t>
+          <t>90709</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>136325</t>
+          <t>138582</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>183913</t>
+          <t>183306</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,65%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15163</t>
+          <t>15539</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36772</t>
+          <t>36774</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20289</t>
+          <t>20990</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42335</t>
+          <t>42036</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41626</t>
+          <t>40713</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>70732</t>
+          <t>70980</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>259753</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>295129</t>
+          <t>294912</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>239454</t>
+          <t>239021</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>276214</t>
+          <t>275732</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>511711</t>
+          <t>513027</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>563446</t>
+          <t>563080</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,31%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66082</t>
+          <t>64882</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>100712</t>
+          <t>99472</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>73156</t>
+          <t>73610</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>106813</t>
+          <t>108190</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>145274</t>
+          <t>146844</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>193617</t>
+          <t>195559</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,15%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>9717</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27832</t>
+          <t>27138</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14201</t>
+          <t>14638</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33911</t>
+          <t>32962</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27504</t>
+          <t>27749</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54146</t>
+          <t>56115</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>335088</t>
+          <t>335460</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>378049</t>
+          <t>377081</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>112790</t>
+          <t>112030</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>135991</t>
+          <t>135819</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>457120</t>
+          <t>456928</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>507172</t>
+          <t>508493</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,91%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>118328</t>
+          <t>116664</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>158314</t>
+          <t>157286</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17689</t>
+          <t>18585</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38032</t>
+          <t>39236</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>142700</t>
+          <t>141352</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>189125</t>
+          <t>188232</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,36%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18153</t>
+          <t>18983</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40081</t>
+          <t>38408</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>7421</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22700</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30113</t>
+          <t>30019</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54195</t>
+          <t>55155</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>768268</t>
+          <t>768334</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>829994</t>
+          <t>832269</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>565613</t>
+          <t>564535</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>619786</t>
+          <t>618460</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1351595</t>
+          <t>1355187</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1433297</t>
+          <t>1435614</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,71%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>256591</t>
+          <t>256469</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>319271</t>
+          <t>315898</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>148724</t>
+          <t>150757</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>197999</t>
+          <t>201693</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>423749</t>
+          <t>423735</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>499522</t>
+          <t>495621</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47050</t>
+          <t>47555</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>78037</t>
+          <t>79608</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>45880</t>
+          <t>46579</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>78955</t>
+          <t>77711</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>100156</t>
+          <t>101509</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>142033</t>
+          <t>143411</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>417226</t>
+          <t>414808</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>464107</t>
+          <t>463852</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>515594</t>
+          <t>515249</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>566148</t>
+          <t>566451</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>950474</t>
+          <t>945853</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1012581</t>
+          <t>1014904</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,79%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>128453</t>
+          <t>129422</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>171606</t>
+          <t>176144</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>122676</t>
+          <t>124208</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>167573</t>
+          <t>167820</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>267782</t>
+          <t>267696</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>326748</t>
+          <t>331583</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,44%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19794</t>
+          <t>20105</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43778</t>
+          <t>41729</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35943</t>
+          <t>35851</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64348</t>
+          <t>62835</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60350</t>
+          <t>60735</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>95344</t>
+          <t>96633</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>191588</t>
+          <t>191898</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>221742</t>
+          <t>222082</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>721705</t>
+          <t>721876</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>786327</t>
+          <t>783647</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>924205</t>
+          <t>928509</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>994708</t>
+          <t>996399</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,91%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>50627</t>
+          <t>50126</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>79193</t>
+          <t>78929</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>241794</t>
+          <t>242964</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>301026</t>
+          <t>299896</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>304017</t>
+          <t>304642</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>366750</t>
+          <t>370793</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7508</t>
+          <t>7931</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23159</t>
+          <t>24019</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>41683</t>
+          <t>41072</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>74402</t>
+          <t>73539</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>55147</t>
+          <t>52556</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>90492</t>
+          <t>88471</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2353448</t>
+          <t>2352725</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2454858</t>
+          <t>2458519</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2463149</t>
+          <t>2457286</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2570979</t>
+          <t>2567581</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4839416</t>
+          <t>4839347</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4995803</t>
+          <t>4996466</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,32%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>759355</t>
+          <t>757931</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>855164</t>
+          <t>856629</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>728502</t>
+          <t>731182</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>827755</t>
+          <t>832553</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1513536</t>
+          <t>1514194</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1655206</t>
+          <t>1655403</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>147709</t>
+          <t>147569</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>199095</t>
+          <t>202279</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>201538</t>
+          <t>200396</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>262285</t>
+          <t>259090</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>366629</t>
+          <t>367025</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>443305</t>
+          <t>447222</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2023</t>
+          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>343327</t>
+          <t>342782</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>384711</t>
+          <t>385357</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>327079</t>
+          <t>327593</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>357807</t>
+          <t>358603</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>679226</t>
+          <t>680273</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>732780</t>
+          <t>733622</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,11%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94545</t>
+          <t>94759</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>132626</t>
+          <t>133383</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61378</t>
+          <t>60346</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>88921</t>
+          <t>88427</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>165604</t>
+          <t>162879</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>212615</t>
+          <t>211787</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,26%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17988</t>
+          <t>17883</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39998</t>
+          <t>38426</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21119</t>
+          <t>21084</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38807</t>
+          <t>39338</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44295</t>
+          <t>43910</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>71291</t>
+          <t>71015</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>331190</t>
+          <t>332125</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>367127</t>
+          <t>368459</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>257538</t>
+          <t>255919</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>288466</t>
+          <t>286685</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>598843</t>
+          <t>598917</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>645766</t>
+          <t>645296</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,3%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63717</t>
+          <t>63053</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>96872</t>
+          <t>94987</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65076</t>
+          <t>65400</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>94322</t>
+          <t>93714</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>136276</t>
+          <t>137721</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>178969</t>
+          <t>179314</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14886</t>
+          <t>15458</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35087</t>
+          <t>33908</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22171</t>
+          <t>23292</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41071</t>
+          <t>41385</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42954</t>
+          <t>42463</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70028</t>
+          <t>67557</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11923,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>485435</t>
+          <t>477683</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>628997</t>
+          <t>623847</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>114830</t>
+          <t>114990</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>133816</t>
+          <t>134616</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>607918</t>
+          <t>612090</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>771463</t>
+          <t>761728</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>91,21%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28313</t>
+          <t>34407</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>138881</t>
+          <t>144890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24782</t>
+          <t>24434</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42572</t>
+          <t>42884</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47269</t>
+          <t>53115</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>173581</t>
+          <t>170430</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47873</t>
+          <t>50876</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14543</t>
+          <t>14310</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15318</t>
+          <t>15602</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56910</t>
+          <t>58354</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>788651</t>
+          <t>783481</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>845521</t>
+          <t>846273</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>308582</t>
+          <t>368675</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>779415</t>
+          <t>782031</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1039920</t>
+          <t>1013160</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1604063</t>
+          <t>1606202</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,88%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>143056</t>
+          <t>144681</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>194227</t>
+          <t>196785</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>143726</t>
+          <t>141976</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>640302</t>
+          <t>579544</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>309212</t>
+          <t>308287</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>912848</t>
+          <t>938723</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>46,68%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32337</t>
+          <t>31504</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>78542</t>
+          <t>76175</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20963</t>
+          <t>22297</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>61889</t>
+          <t>61293</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>63793</t>
+          <t>61682</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>119611</t>
+          <t>119726</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,7 +12690,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>359930</t>
+          <t>359249</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>395336</t>
+          <t>397403</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>655026</t>
+          <t>655334</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>716739</t>
+          <t>722537</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1026737</t>
+          <t>1027133</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1104207</t>
+          <t>1108409</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,3%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>54478</t>
+          <t>53563</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>87062</t>
+          <t>87155</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,82 +12963,82 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
+          <t>11,28%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>18,35%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>118479</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>89011</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>141932</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>14,11%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>10,6%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>16,9%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>187406</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>150855</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>215586</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>14,25%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>11,47%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>18,33%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>118479</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>91330</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>140834</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>14,11%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>10,87%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>16,77%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>187406</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>153645</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>216930</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>14,25%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>11,68%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18818</t>
+          <t>18949</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40421</t>
+          <t>38817</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27902</t>
+          <t>26349</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51054</t>
+          <t>52210</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52285</t>
+          <t>51387</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>83558</t>
+          <t>84964</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>175705</t>
+          <t>177579</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>216528</t>
+          <t>216103</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>569730</t>
+          <t>572304</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>616368</t>
+          <t>617935</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>764227</t>
+          <t>767749</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>822895</t>
+          <t>823863</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,23%</t>
         </is>
       </c>
     </row>
@@ -13404,12 +13404,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13925</t>
+          <t>13563</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>46738</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>112825</t>
+          <t>110981</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>155476</t>
+          <t>154826</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>134028</t>
+          <t>134409</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>186585</t>
+          <t>185448</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -13517,12 +13517,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5497</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27665</t>
+          <t>28487</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>24584</t>
+          <t>24615</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>47858</t>
+          <t>47941</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>34829</t>
+          <t>34482</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>66479</t>
+          <t>66552</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2592863</t>
+          <t>2591063</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2820356</t>
+          <t>2830635</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2092426</t>
+          <t>2139556</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2807550</t>
+          <t>2807702</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4795973</t>
+          <t>4594096</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5514364</t>
+          <t>5496760</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,1%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>423357</t>
+          <t>417523</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>600936</t>
+          <t>606709</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>570660</t>
+          <t>572757</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1325675</t>
+          <t>1287568</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1088559</t>
+          <t>1099812</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1843482</t>
+          <t>2001640</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>128130</t>
+          <t>131170</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>201070</t>
+          <t>203337</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>149912</t>
+          <t>154148</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>215281</t>
+          <t>215565</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>299768</t>
+          <t>298205</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>397462</t>
+          <t>401177</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P05A01-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P05A01-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>208235</t>
+          <t>209240</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>252877</t>
+          <t>251164</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>131065</t>
+          <t>133245</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>166928</t>
+          <t>167028</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>351811</t>
+          <t>353398</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>408924</t>
+          <t>409405</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,51%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>155509</t>
+          <t>157679</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>198115</t>
+          <t>200471</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>101433</t>
+          <t>100354</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>135646</t>
+          <t>133408</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>263790</t>
+          <t>267426</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>322363</t>
+          <t>321280</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,21%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51301</t>
+          <t>51651</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>82170</t>
+          <t>81962</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28624</t>
+          <t>29592</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52078</t>
+          <t>53008</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>88608</t>
+          <t>87033</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>127356</t>
+          <t>128262</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>175131</t>
+          <t>172599</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>213927</t>
+          <t>212513</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>156777</t>
+          <t>155692</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>194961</t>
+          <t>193055</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>342186</t>
+          <t>341156</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>398728</t>
+          <t>398923</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>54,07%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>118585</t>
+          <t>117707</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>156423</t>
+          <t>155581</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>127931</t>
+          <t>129075</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>165643</t>
+          <t>165733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>256439</t>
+          <t>251892</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>308196</t>
+          <t>309677</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>41,97%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26144</t>
+          <t>27276</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49838</t>
+          <t>49923</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37178</t>
+          <t>37384</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63721</t>
+          <t>62166</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67558</t>
+          <t>69573</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104752</t>
+          <t>104669</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>257591</t>
+          <t>257518</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>307955</t>
+          <t>304074</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>75566</t>
+          <t>75739</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>102469</t>
+          <t>102120</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>345033</t>
+          <t>345087</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>400035</t>
+          <t>398576</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,12%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>185521</t>
+          <t>186334</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>233276</t>
+          <t>231728</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37099</t>
+          <t>38224</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60552</t>
+          <t>60382</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>227858</t>
+          <t>230311</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>282302</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,75%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>39617</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67309</t>
+          <t>66654</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21676</t>
+          <t>21156</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>41781</t>
+          <t>40984</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66597</t>
+          <t>66382</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>102252</t>
+          <t>100746</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>604943</t>
+          <t>601821</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>673814</t>
+          <t>674118</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>321765</t>
+          <t>323139</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>377964</t>
+          <t>379185</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>946036</t>
+          <t>945229</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1034367</t>
+          <t>1034634</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,04%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>448563</t>
+          <t>450042</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>515243</t>
+          <t>515971</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>231618</t>
+          <t>229718</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>282901</t>
+          <t>280751</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>697433</t>
+          <t>697712</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>781099</t>
+          <t>781348</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,05%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96069</t>
+          <t>95488</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>138700</t>
+          <t>136809</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>89467</t>
+          <t>88322</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>127755</t>
+          <t>127029</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>193312</t>
+          <t>197292</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>251498</t>
+          <t>252185</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>191486</t>
+          <t>190475</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>230438</t>
+          <t>229108</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>270604</t>
+          <t>271194</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>319552</t>
+          <t>320450</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>480054</t>
+          <t>474010</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>539689</t>
+          <t>536731</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,44%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>88087</t>
+          <t>86930</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>122013</t>
+          <t>123038</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>177462</t>
+          <t>176386</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>222041</t>
+          <t>221903</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>275906</t>
+          <t>275297</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>332727</t>
+          <t>332662</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24258</t>
+          <t>24811</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47265</t>
+          <t>47792</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>56612</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>90702</t>
+          <t>89088</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>88348</t>
+          <t>87402</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>128194</t>
+          <t>126439</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,77%</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>155225</t>
+          <t>154480</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>187643</t>
+          <t>187242</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>602934</t>
+          <t>604637</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>670810</t>
+          <t>671909</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>768748</t>
+          <t>768268</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>845267</t>
+          <t>845952</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,72%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>88843</t>
+          <t>88851</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>120854</t>
+          <t>120216</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>422018</t>
+          <t>422546</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>487805</t>
+          <t>488367</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>524346</t>
+          <t>524952</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>595530</t>
+          <t>599677</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,79%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15570</t>
+          <t>15705</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>35424</t>
+          <t>32976</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>134052</t>
+          <t>133072</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>178955</t>
+          <t>180269</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>154539</t>
+          <t>155846</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>205091</t>
+          <t>204591</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1671489</t>
+          <t>1673678</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1781747</t>
+          <t>1789153</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1642543</t>
+          <t>1639505</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1754441</t>
+          <t>1752443</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3335901</t>
+          <t>3346997</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3507663</t>
+          <t>3503020</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,73%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1164497</t>
+          <t>1161387</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1271006</t>
+          <t>1268113</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1167844</t>
+          <t>1163778</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1277927</t>
+          <t>1276895</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2352707</t>
+          <t>2352579</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2512033</t>
+          <t>2515122</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,86%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>292771</t>
+          <t>293837</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>363188</t>
+          <t>364193</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>417152</t>
+          <t>417630</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>493668</t>
+          <t>499140</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>726108</t>
+          <t>726780</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>832145</t>
+          <t>831708</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>255060</t>
+          <t>256929</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>298295</t>
+          <t>297967</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>211545</t>
+          <t>210378</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>243288</t>
+          <t>243609</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>479857</t>
+          <t>478797</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>533997</t>
+          <t>533757</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,01%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>105094</t>
+          <t>106965</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>146280</t>
+          <t>146222</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52990</t>
+          <t>51826</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84040</t>
+          <t>82600</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>167971</t>
+          <t>166929</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>219649</t>
+          <t>217252</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24559</t>
+          <t>22865</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47374</t>
+          <t>45428</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12749</t>
+          <t>12306</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29208</t>
+          <t>29878</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40860</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>68246</t>
+          <t>70254</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>256575</t>
+          <t>254872</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>298310</t>
+          <t>298801</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>214601</t>
+          <t>213497</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>249110</t>
+          <t>249744</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>482175</t>
+          <t>482811</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>536478</t>
+          <t>538451</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>71,31%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>95555</t>
+          <t>96067</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>137093</t>
+          <t>136668</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>57742</t>
+          <t>59742</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>88966</t>
+          <t>89375</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>163146</t>
+          <t>163291</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>212876</t>
+          <t>212465</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,14%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15885</t>
+          <t>15960</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38570</t>
+          <t>40054</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20845</t>
+          <t>20583</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44527</t>
+          <t>45455</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43326</t>
+          <t>42848</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75997</t>
+          <t>76836</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>407386</t>
+          <t>407704</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>456349</t>
+          <t>455558</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>162526</t>
+          <t>162707</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>193143</t>
+          <t>192890</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>582044</t>
+          <t>580281</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>639744</t>
+          <t>639438</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,16%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>134119</t>
+          <t>133444</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>178794</t>
+          <t>177655</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44781</t>
+          <t>44769</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72787</t>
+          <t>72755</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>184872</t>
+          <t>187504</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>240431</t>
+          <t>241579</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,26%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28300</t>
+          <t>28245</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55063</t>
+          <t>54032</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15116</t>
+          <t>15261</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33789</t>
+          <t>34441</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>48765</t>
+          <t>47228</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>79472</t>
+          <t>82081</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>777584</t>
+          <t>773940</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>839355</t>
+          <t>840662</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>511685</t>
+          <t>509981</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>565195</t>
+          <t>561759</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1298261</t>
+          <t>1301621</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1386064</t>
+          <t>1387032</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,21%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>243921</t>
+          <t>243136</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>301376</t>
+          <t>301393</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>154105</t>
+          <t>155228</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203621</t>
+          <t>202157</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>413240</t>
+          <t>411535</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>491778</t>
+          <t>490110</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,52%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58695</t>
+          <t>58443</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>94517</t>
+          <t>95070</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37686</t>
+          <t>36668</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>66573</t>
+          <t>66049</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>104161</t>
+          <t>103874</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>150996</t>
+          <t>147775</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>348655</t>
+          <t>341639</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>388491</t>
+          <t>387919</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>526593</t>
+          <t>525913</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>577647</t>
+          <t>576100</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>886305</t>
+          <t>886808</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>950263</t>
+          <t>950330</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>93675</t>
+          <t>93867</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>132258</t>
+          <t>133341</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>135945</t>
+          <t>136368</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>181943</t>
+          <t>182882</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>241734</t>
+          <t>240677</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>303855</t>
+          <t>300586</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,65%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20328</t>
+          <t>21598</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41965</t>
+          <t>43448</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37206</t>
+          <t>37343</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>66527</t>
+          <t>66330</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64127</t>
+          <t>64820</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>100147</t>
+          <t>99103</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>158257</t>
+          <t>158123</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>189334</t>
+          <t>188719</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>732123</t>
+          <t>731671</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>790747</t>
+          <t>792407</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>901331</t>
+          <t>899247</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>970132</t>
+          <t>970469</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,57%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>67258</t>
+          <t>65291</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>97642</t>
+          <t>96645</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>255755</t>
+          <t>254841</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>311875</t>
+          <t>313134</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>332509</t>
+          <t>332516</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>397845</t>
+          <t>399337</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20338</t>
+          <t>20166</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>46798</t>
+          <t>48373</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>78129</t>
+          <t>79051</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>59046</t>
+          <t>59347</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>92285</t>
+          <t>91785</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2283773</t>
+          <t>2279673</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2389247</t>
+          <t>2396166</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2432946</t>
+          <t>2431048</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2545034</t>
+          <t>2540155</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4752532</t>
+          <t>4753314</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4912214</t>
+          <t>4906066</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,49%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>807569</t>
+          <t>804772</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>910796</t>
+          <t>913538</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>769541</t>
+          <t>771361</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>871981</t>
+          <t>871825</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1608738</t>
+          <t>1606512</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1751928</t>
+          <t>1749783</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>189913</t>
+          <t>187889</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>250652</t>
+          <t>244708</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>207912</t>
+          <t>207711</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>268907</t>
+          <t>268160</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>412848</t>
+          <t>411922</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>495219</t>
+          <t>496342</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>300546</t>
+          <t>299381</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>339167</t>
+          <t>337375</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>223536</t>
+          <t>223822</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>259287</t>
+          <t>258535</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>534066</t>
+          <t>534202</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>586777</t>
+          <t>585634</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,56%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68908</t>
+          <t>68600</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>102873</t>
+          <t>103996</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59006</t>
+          <t>58551</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90709</t>
+          <t>89495</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>138582</t>
+          <t>137887</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>183306</t>
+          <t>183839</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15539</t>
+          <t>15807</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36774</t>
+          <t>36651</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20990</t>
+          <t>20847</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42036</t>
+          <t>41634</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>40713</t>
+          <t>41446</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>70980</t>
+          <t>72526</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>261052</t>
+          <t>261586</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>294912</t>
+          <t>295842</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>239021</t>
+          <t>240580</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>275732</t>
+          <t>277175</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>513027</t>
+          <t>512335</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>563080</t>
+          <t>564263</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,47%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64882</t>
+          <t>66134</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>99472</t>
+          <t>99931</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>73610</t>
+          <t>72534</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>108190</t>
+          <t>106826</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>146844</t>
+          <t>148144</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>195559</t>
+          <t>194277</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,98%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9717</t>
+          <t>10050</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27138</t>
+          <t>27492</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14638</t>
+          <t>14606</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32962</t>
+          <t>33520</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27749</t>
+          <t>28205</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56115</t>
+          <t>54749</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>335460</t>
+          <t>336290</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>377081</t>
+          <t>380662</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>112030</t>
+          <t>111093</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>135819</t>
+          <t>134635</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>456928</t>
+          <t>460008</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>508493</t>
+          <t>510575</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>74,21%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>116664</t>
+          <t>114554</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>157286</t>
+          <t>156691</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18585</t>
+          <t>18871</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39236</t>
+          <t>40441</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>141352</t>
+          <t>141418</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>188232</t>
+          <t>186419</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,09%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18983</t>
+          <t>18650</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38408</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7421</t>
+          <t>7491</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22981</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30019</t>
+          <t>28599</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55155</t>
+          <t>54328</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>768334</t>
+          <t>769210</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>832269</t>
+          <t>832026</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>564535</t>
+          <t>568808</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>618460</t>
+          <t>620204</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1355187</t>
+          <t>1352829</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1435614</t>
+          <t>1434206</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,64%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>256469</t>
+          <t>257805</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>315898</t>
+          <t>319380</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>150757</t>
+          <t>148317</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>201693</t>
+          <t>196215</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>423735</t>
+          <t>425598</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>495621</t>
+          <t>500662</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,36%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47555</t>
+          <t>46620</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>79608</t>
+          <t>78620</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>46579</t>
+          <t>44685</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>77711</t>
+          <t>76883</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>101509</t>
+          <t>101151</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>143411</t>
+          <t>144591</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>414808</t>
+          <t>417361</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>463852</t>
+          <t>464349</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>515249</t>
+          <t>516706</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>566451</t>
+          <t>566792</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>945853</t>
+          <t>949438</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1014904</t>
+          <t>1014949</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,8%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>129422</t>
+          <t>128891</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>176144</t>
+          <t>174195</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>124208</t>
+          <t>123692</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>167820</t>
+          <t>168944</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>267696</t>
+          <t>265881</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>331583</t>
+          <t>328335</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20105</t>
+          <t>20068</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41729</t>
+          <t>42296</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35851</t>
+          <t>35997</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62835</t>
+          <t>63079</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60735</t>
+          <t>61655</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>96633</t>
+          <t>97675</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>191898</t>
+          <t>192460</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>222082</t>
+          <t>222142</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>721876</t>
+          <t>722676</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>783647</t>
+          <t>787173</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>928509</t>
+          <t>925771</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>996399</t>
+          <t>995781</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>72,86%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>50126</t>
+          <t>51229</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>78929</t>
+          <t>79192</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>242964</t>
+          <t>238001</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>299896</t>
+          <t>299464</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>304642</t>
+          <t>302319</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>370793</t>
+          <t>368527</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,97%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7931</t>
+          <t>7831</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24019</t>
+          <t>22830</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>41072</t>
+          <t>41852</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>73539</t>
+          <t>74883</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>52556</t>
+          <t>53460</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>88471</t>
+          <t>88630</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2352725</t>
+          <t>2351534</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2458519</t>
+          <t>2459848</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2457286</t>
+          <t>2459533</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2567581</t>
+          <t>2570590</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4839347</t>
+          <t>4843468</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4996466</t>
+          <t>4998685</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>72,35%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>757931</t>
+          <t>752485</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>856629</t>
+          <t>856555</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,7 +10449,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>731182</t>
+          <t>726428</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>832553</t>
+          <t>832117</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1514194</t>
+          <t>1509509</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1655403</t>
+          <t>1653479</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>147569</t>
+          <t>147057</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>202279</t>
+          <t>203530</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>200396</t>
+          <t>202693</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>259090</t>
+          <t>260869</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>367025</t>
+          <t>365738</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>447222</t>
+          <t>443750</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -11006,32 +11006,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>364347</t>
+          <t>396000</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>342782</t>
+          <t>371249</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>385357</t>
+          <t>418510</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11041,32 +11041,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>342746</t>
+          <t>372207</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>327593</t>
+          <t>353813</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>358603</t>
+          <t>387763</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11076,32 +11076,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>707092</t>
+          <t>768207</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>680273</t>
+          <t>739238</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>733622</t>
+          <t>794527</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,57%</t>
         </is>
       </c>
     </row>
@@ -11119,32 +11119,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>113349</t>
+          <t>124291</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94759</t>
+          <t>104183</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>133383</t>
+          <t>146546</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11154,32 +11154,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>74197</t>
+          <t>82208</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60346</t>
+          <t>69223</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>88427</t>
+          <t>99345</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11189,32 +11189,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>187546</t>
+          <t>206498</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>162879</t>
+          <t>181829</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>211787</t>
+          <t>232753</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,43%</t>
         </is>
       </c>
     </row>
@@ -11232,32 +11232,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27517</t>
+          <t>30327</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17883</t>
+          <t>20889</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38426</t>
+          <t>42619</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11267,32 +11267,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29182</t>
+          <t>32565</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21084</t>
+          <t>23684</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39338</t>
+          <t>43375</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11302,32 +11302,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>56699</t>
+          <t>62891</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>43910</t>
+          <t>48944</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>71015</t>
+          <t>79755</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -11345,17 +11345,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11380,17 +11380,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>446125</t>
+          <t>486979</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>446125</t>
+          <t>486979</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>446125</t>
+          <t>486979</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11415,17 +11415,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>951337</t>
+          <t>1037597</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>951337</t>
+          <t>1037597</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>951337</t>
+          <t>1037597</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11462,32 +11462,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>350405</t>
+          <t>371977</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>332125</t>
+          <t>352082</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>368459</t>
+          <t>389063</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11497,32 +11497,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>272669</t>
+          <t>301618</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>255919</t>
+          <t>285114</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>286685</t>
+          <t>318656</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11532,32 +11532,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>623075</t>
+          <t>673595</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>598917</t>
+          <t>647630</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>645296</t>
+          <t>700897</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,33%</t>
         </is>
       </c>
     </row>
@@ -11575,32 +11575,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>78851</t>
+          <t>86745</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63053</t>
+          <t>71254</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>94987</t>
+          <t>104848</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11610,32 +11610,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>78634</t>
+          <t>86395</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65400</t>
+          <t>71760</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93714</t>
+          <t>101862</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11645,32 +11645,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>157485</t>
+          <t>173140</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>137721</t>
+          <t>150795</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>179314</t>
+          <t>197301</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -11688,32 +11688,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22957</t>
+          <t>24490</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15458</t>
+          <t>16277</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33908</t>
+          <t>36579</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>31277</t>
+          <t>35130</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23292</t>
+          <t>26109</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41385</t>
+          <t>45562</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>54234</t>
+          <t>59620</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42463</t>
+          <t>46228</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67557</t>
+          <t>76189</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -11801,17 +11801,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11836,17 +11836,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11918,32 +11918,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>556124</t>
+          <t>344527</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>477683</t>
+          <t>320067</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>623847</t>
+          <t>364466</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11953,32 +11953,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>125109</t>
+          <t>140910</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>114990</t>
+          <t>130465</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>134616</t>
+          <t>150949</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11988,32 +11988,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>681233</t>
+          <t>485437</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>612090</t>
+          <t>457034</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>761728</t>
+          <t>505569</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>76,7%</t>
         </is>
       </c>
     </row>
@@ -12031,32 +12031,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>84284</t>
+          <t>98696</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34407</t>
+          <t>80598</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>144890</t>
+          <t>120205</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>36655</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24434</t>
+          <t>28060</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42884</t>
+          <t>47977</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>116981</t>
+          <t>135351</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53115</t>
+          <t>116433</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>170430</t>
+          <t>159722</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>24,23%</t>
         </is>
       </c>
     </row>
@@ -12144,32 +12144,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>27856</t>
+          <t>28389</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>19089</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50876</t>
+          <t>41501</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12179,32 +12179,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>9931</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>5620</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14310</t>
+          <t>16125</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>36961</t>
+          <t>38320</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15602</t>
+          <t>28023</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>58354</t>
+          <t>52401</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -12257,17 +12257,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12374,22 +12374,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>817505</t>
+          <t>886342</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>783481</t>
+          <t>856338</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>846273</t>
+          <t>917810</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12409,32 +12409,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>611675</t>
+          <t>675982</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>368675</t>
+          <t>651832</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>782031</t>
+          <t>694726</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12444,32 +12444,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1429179</t>
+          <t>1562324</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1013160</t>
+          <t>1521921</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1606202</t>
+          <t>1596199</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>80,21%</t>
         </is>
       </c>
     </row>
@@ -12487,32 +12487,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>169105</t>
+          <t>195677</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>144681</t>
+          <t>165978</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>196785</t>
+          <t>223597</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12522,32 +12522,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>323053</t>
+          <t>134830</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>141976</t>
+          <t>116770</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>579544</t>
+          <t>156487</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12557,32 +12557,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>492157</t>
+          <t>330507</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>308287</t>
+          <t>297809</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>938723</t>
+          <t>366905</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -12600,22 +12600,22 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>46192</t>
+          <t>46775</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31504</t>
+          <t>34436</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>76175</t>
+          <t>61960</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -12625,7 +12625,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12635,32 +12635,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>43366</t>
+          <t>50399</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22297</t>
+          <t>39353</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>61293</t>
+          <t>64180</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12670,32 +12670,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>89558</t>
+          <t>97174</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>61682</t>
+          <t>79873</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>119726</t>
+          <t>116145</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1032801</t>
+          <t>1128794</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1032801</t>
+          <t>1128794</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1032801</t>
+          <t>1128794</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12748,17 +12748,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2010894</t>
+          <t>1990005</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2010894</t>
+          <t>1990005</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2010894</t>
+          <t>1990005</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12830,32 +12830,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>378083</t>
+          <t>452535</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>359249</t>
+          <t>430484</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>397403</t>
+          <t>473085</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12865,32 +12865,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>682046</t>
+          <t>645775</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>655334</t>
+          <t>624992</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>722537</t>
+          <t>666283</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12900,32 +12900,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1060129</t>
+          <t>1098311</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1027133</t>
+          <t>1067974</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1108409</t>
+          <t>1129228</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>80,82%</t>
         </is>
       </c>
     </row>
@@ -12943,32 +12943,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>68928</t>
+          <t>84237</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>53563</t>
+          <t>66622</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>87155</t>
+          <t>103930</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12978,32 +12978,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>118479</t>
+          <t>135681</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>89011</t>
+          <t>117561</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>141932</t>
+          <t>155974</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13013,32 +13013,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>187406</t>
+          <t>219918</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>150855</t>
+          <t>192806</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>215586</t>
+          <t>246124</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>17,62%</t>
         </is>
       </c>
     </row>
@@ -13056,32 +13056,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>28035</t>
+          <t>31192</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18949</t>
+          <t>21757</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38817</t>
+          <t>44829</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13091,32 +13091,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>39334</t>
+          <t>47797</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26349</t>
+          <t>36539</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52210</t>
+          <t>59304</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>67369</t>
+          <t>78989</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51387</t>
+          <t>64822</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84964</t>
+          <t>96737</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -13169,17 +13169,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>839858</t>
+          <t>829254</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>839858</t>
+          <t>829254</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>839858</t>
+          <t>829254</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13239,17 +13239,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1314904</t>
+          <t>1397218</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1314904</t>
+          <t>1397218</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1314904</t>
+          <t>1397218</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13286,32 +13286,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>200718</t>
+          <t>197281</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>177579</t>
+          <t>174203</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>216103</t>
+          <t>211500</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13321,32 +13321,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>594920</t>
+          <t>658754</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>572304</t>
+          <t>633535</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>617935</t>
+          <t>681476</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13356,32 +13356,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>795638</t>
+          <t>856035</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>767749</t>
+          <t>822362</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>823863</t>
+          <t>884774</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>81,81%</t>
         </is>
       </c>
     </row>
@@ -13399,32 +13399,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>27132</t>
+          <t>26678</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13563</t>
+          <t>15107</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46738</t>
+          <t>48096</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13434,32 +13434,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>131631</t>
+          <t>144745</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>110981</t>
+          <t>124019</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>154826</t>
+          <t>168237</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13469,17 +13469,17 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>158763</t>
+          <t>171423</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>134409</t>
+          <t>147041</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>185448</t>
+          <t>199308</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -13512,32 +13512,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>12657</t>
+          <t>13269</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5497</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>28487</t>
+          <t>27017</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13547,32 +13547,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>34819</t>
+          <t>40782</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>24615</t>
+          <t>29186</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>47941</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13582,32 +13582,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>47477</t>
+          <t>54051</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>34482</t>
+          <t>40764</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>66552</t>
+          <t>73828</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -13625,17 +13625,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13660,17 +13660,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13695,17 +13695,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13742,32 +13742,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2667181</t>
+          <t>2648662</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2591063</t>
+          <t>2592684</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2830635</t>
+          <t>2705590</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13777,32 +13777,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2629165</t>
+          <t>2795247</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2139556</t>
+          <t>2747455</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2807702</t>
+          <t>2838398</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13812,32 +13812,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>5296346</t>
+          <t>5443909</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4594096</t>
+          <t>5378309</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5496760</t>
+          <t>5515719</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>78,0%</t>
         </is>
       </c>
     </row>
@@ -13855,32 +13855,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>541647</t>
+          <t>616323</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>417523</t>
+          <t>569709</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>606709</t>
+          <t>670599</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13890,32 +13890,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>758690</t>
+          <t>620514</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>572757</t>
+          <t>581070</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1287568</t>
+          <t>664102</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13925,32 +13925,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1300338</t>
+          <t>1236838</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1099812</t>
+          <t>1171946</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2001640</t>
+          <t>1299793</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -13968,102 +13968,102 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>165214</t>
+          <t>174441</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>131170</t>
+          <t>146362</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>203337</t>
+          <t>202933</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>216603</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>192193</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>244392</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>5,96%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>5,29%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>6,73%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>457</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>391045</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>351863</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>426294</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
           <t>6,03%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>187083</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>154148</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>215565</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>5,23%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>457</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>352297</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>298205</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>401177</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -14081,17 +14081,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3374042</t>
+          <t>3439427</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3374042</t>
+          <t>3439427</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3374042</t>
+          <t>3439427</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14116,17 +14116,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3574938</t>
+          <t>3632365</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3574938</t>
+          <t>3632365</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3574938</t>
+          <t>3632365</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14151,17 +14151,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6948981</t>
+          <t>7071792</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6948981</t>
+          <t>7071792</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6948981</t>
+          <t>7071792</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
